--- a/output/central_unit_requests/GCE - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/GCE - SR26 sustainability reporting request.xlsx
@@ -627,7 +627,7 @@
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col hidden="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="24" customWidth="1" min="11" max="11"/>
@@ -648,7 +648,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting (v0.12)</t>
+          <t>End-2026 target status assessment and reporting (v0.13)</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>End-2025 reporting (click the ref to see your full SR25 response)</t>
+          <t>SR25 response</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
@@ -1017,9 +1017,8 @@
     <row r="18"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="M7:N7"/>
-    <mergeCell ref="H13:K13"/>
     <mergeCell ref="B4:C8"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="L13:R13"/>

--- a/output/central_unit_requests/GCE - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/GCE - SR26 sustainability reporting request.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,18 +78,6 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <i val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
       <sz val="22"/>
@@ -125,8 +113,12 @@
       <sz val="11"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -146,11 +138,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C1E4F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -191,38 +178,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -238,9 +218,10 @@
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -617,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -631,13 +612,12 @@
     <col hidden="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="24" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -648,350 +628,277 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting (v0.13)</t>
+          <t>SR26 sustainability reporting (v0.14)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>End-2026 target status confirmation and reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>Target status assessment and definitions</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="B4" s="5" t="inlineStr">
+          <t>SR26 sustainability reporting request</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>• Confirm target status for each row below (Column L). Refer to target status definitions to the right for guidance.
-• Provide commentary on progress towards each target (Column M or N)
-• Provide supporting documentation if required (Column O), including links to images
-• Note the source of your information and any limitations (Column P), then confirm the information is accurate (Columns Q–R)
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
+• Provide supporting information if required (Column N), including links to documents or images
+• Note the source of your information and any limitations (Column O), then confirm the information is accurate (Columns P–Q)
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
-• 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch.
+• 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
 • Due: Tuesday 15 December 2026. Questions: CDSS – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr">
-        <is>
-          <t>The data and information provided demonstrates that the Faculty/Portfolio has met or exceeded the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>The data and information provided indicates that the target has not been met, but there has been a significant improvement and performance is trending towards the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>Some action has been taken to address the target, but the data and information provided demonstrates that this has been insufficient to meet the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>No action has been taken.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="L8" s="9" t="n"/>
-    </row>
-    <row r="9">
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>Note: target status definitions are under review for 2027 reporting. 2026 ratings are for internal management reporting only.</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8" ht="60" customHeight="1"/>
     <row r="11">
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>GCE – Global, Culture and Engagement</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="13" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="14" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="15" t="inlineStr">
-        <is>
-          <t>Confirm end-2026 target status</t>
-        </is>
-      </c>
-      <c r="M14" s="15" t="inlineStr">
+      <c r="L14" s="10" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="N14" s="15" t="inlineStr">
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="O14" s="15" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="P14" s="15" t="inlineStr">
+      <c r="O14" s="10" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="Q14" s="15" t="inlineStr">
+      <c r="P14" s="10" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="R14" s="15" t="inlineStr">
+      <c r="Q14" s="10" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="16" t="inlineStr"/>
-      <c r="C15" s="16" t="inlineStr"/>
-      <c r="D15" s="16" t="inlineStr"/>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="16" t="inlineStr"/>
-      <c r="H15" s="16" t="inlineStr"/>
-      <c r="I15" s="16" t="inlineStr"/>
-      <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>(Met or exceeded; partially met; not met; not yet started)</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-A general update on activities in relation to the overarching target (Column D)</t>
-        </is>
-      </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-Data and commentary in direct response to the reporting request (Column F)</t>
-        </is>
-      </c>
-      <c r="O15" s="16" t="inlineStr">
-        <is>
-          <t>Provide any additional information to support the target status assessment (e.g. links, images, rationale for selection of target status)</t>
-        </is>
-      </c>
-      <c r="P15" s="16" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr"/>
+      <c r="C15" s="11" t="inlineStr"/>
+      <c r="D15" s="11" t="inlineStr"/>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr"/>
+      <c r="G15" s="11" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr"/>
+      <c r="I15" s="11" t="inlineStr"/>
+      <c r="J15" s="11" t="inlineStr"/>
+      <c r="K15" s="11" t="inlineStr"/>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>A general update on activities in relation to the overarching target (Column D)</t>
+        </is>
+      </c>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Data and commentary in direct response to the reporting request (Column F)</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Any additional information (e.g. links, images, documents)</t>
+        </is>
+      </c>
+      <c r="O15" s="11" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="Q15" s="16" t="inlineStr">
+      <c r="P15" s="11" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="R15" s="16" t="inlineStr">
+      <c r="Q15" s="11" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Evidence of sustainability outcomes informed by Indigenous knowledges</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>Please provide examples or case studies from your Faculty/Portfolio of sustainability outcomes informed by Indigenous knowledges. Describe the activity or decision, how Indigenous knowledges were incorporated or co-created, who was involved, and the resulting sustainability outcome.</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>We will report on the ways Indigenous knowledges inform sustainability activities across the University, and develop selected examples into case studies with appropriate permissions.</t>
         </is>
       </c>
-      <c r="H16" s="19" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I16" s="19" t="inlineStr"/>
-      <c r="J16" s="19" t="inlineStr"/>
-      <c r="K16" s="19" t="inlineStr"/>
-      <c r="L16" s="20" t="n"/>
-      <c r="M16" s="20" t="n"/>
-      <c r="N16" s="20" t="n"/>
-      <c r="O16" s="20" t="n"/>
-      <c r="P16" s="20" t="n"/>
-      <c r="Q16" s="20" t="n"/>
-      <c r="R16" s="20" t="n"/>
+      <c r="I16" s="14" t="inlineStr"/>
+      <c r="J16" s="14" t="inlineStr"/>
+      <c r="K16" s="14" t="inlineStr"/>
+      <c r="L16" s="15" t="n"/>
+      <c r="M16" s="15" t="n"/>
+      <c r="N16" s="15" t="n"/>
+      <c r="O16" s="15" t="n"/>
+      <c r="P16" s="15" t="n"/>
+      <c r="Q16" s="15" t="n"/>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your area reported on the related SP2030 target 7c(ii) and rated it 'Met or exceeded' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your area reported on the related SP2030 target 7c(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr">
+      <c r="H17" s="16" t="inlineStr">
         <is>
           <t>7c(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I17" s="19" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J17" s="19" t="inlineStr">
+      <c r="J17" s="14" t="inlineStr">
         <is>
           <t>Strengthened engagement with the Pacific region
 Throughout 2025, the University strengthened its engagement with institutions and communities with our closest neighbours in the Pacific. Drawing on the expertise and focus of leading initiatives such as the Oceania Institute and Melbourne Climate Futures, the University continued to work with regional partners to address the distinct challenges faced by the Pacific region. 
@@ -999,40 +906,31 @@
 Key convening moments in 2025 have included the delivery of the Asia and the Pacific Outlook Series in Honiara, the Oceania Institute Conversations series in Melbourne and the inaugural Oceania Oration delivered by The Honourable Professor Biman Prasad, Deputy Prime Minister of Fiji in August. His address called for reframing perspectives on the Pacific, strengthening regional partnerships, and addressing climate and development challenges collaboratively.</t>
         </is>
       </c>
-      <c r="K17" s="19" t="inlineStr">
+      <c r="K17" s="14" t="inlineStr">
         <is>
           <t>https://www.unimelb.edu.au/newsroom/news/2025/march/university-of-melbourne-leads-engagement-with-the-pacific-through-education-and-research
 https://www.unimelb.edu.au/newsroom/news/2025/february/university-of-melbourne-strengthens-ties-with-pacific
 https://www.unimelb.edu.au/newsroom/news/2025/august/university-of-melbourne-hosts-inaugural-oceania-oration-on-pacific-futures</t>
         </is>
       </c>
-      <c r="L17" s="20" t="n"/>
-      <c r="M17" s="20" t="n"/>
-      <c r="N17" s="20" t="n"/>
-      <c r="O17" s="20" t="n"/>
-      <c r="P17" s="20" t="n"/>
-      <c r="Q17" s="20" t="n"/>
-      <c r="R17" s="20" t="n"/>
+      <c r="L17" s="15" t="n"/>
+      <c r="M17" s="15" t="n"/>
+      <c r="N17" s="15" t="n"/>
+      <c r="O17" s="15" t="n"/>
+      <c r="P17" s="15" t="n"/>
+      <c r="Q17" s="15" t="n"/>
     </row>
     <row r="18"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="9">
-    <mergeCell ref="M7:N7"/>
+  <mergeCells count="4">
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="D4:G8"/>
     <mergeCell ref="B4:C8"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="L13:R13"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="D4:G8"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="L16:L17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$B$3:$B$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="Q16:Q17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
+  <dataValidations count="1">
+    <dataValidation sqref="P16:P17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
       <formula1>=Lists!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -1072,7 +970,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting</t>
+          <t>SR26 sustainability reporting</t>
         </is>
       </c>
     </row>
@@ -1084,12 +982,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
         </is>
@@ -1097,77 +995,77 @@
     </row>
     <row r="6"/>
     <row r="8">
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="24" t="inlineStr"/>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr"/>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="20" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="20" t="n"/>
-      <c r="F10" s="20" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="20" t="n"/>
-      <c r="C11" s="20" t="n"/>
-      <c r="D11" s="20" t="n"/>
-      <c r="E11" s="20" t="n"/>
-      <c r="F11" s="20" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1218,88 +1116,88 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Chancellery Global, Culture and Engagement</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>7a</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>The University’s community partnerships demonstrate localised and co-created approaches to sustainability.</t>
         </is>
       </c>
-      <c r="D7" s="19" t="e">
+      <c r="D7" s="14" t="e">
         <v>#REF!</v>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>Grounded in hyper local collaboration and partnerships the University's civic and community initiatives respond to and address key issues identified by communities and includes the following. 
 *Co- leading  a five-year collective action initiative to address  food security challenges  in Carlton, co-designing and evaluating programs with residents and local organisations. 
@@ -1309,38 +1207,38 @@
  *Supporting  the digital equity initiative in collaboration with UoM E-Waste to donate a further 33 iPads to community organisations. Work is underway to expand this program with the support of Business Services.                                                                                                                     *Employing social procurement and sustainability practices in Civic and Community Engagement program delivery. E.g. Choose to Reuse, social enterprise catering, bicycle couriers, online presentations to offset travel.</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr"/>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr"/>
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>https://www.innercitynews.com.au/tackling-hunger-in-carlton/
 https://about.unimelb.edu.au/news-resources/awards-and-achievements/announcements/university-of-melbourne-and-carlton-community-partner-to-enhance-local-food-security/_recache</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr"/>
+      <c r="I7" s="14" t="inlineStr"/>
     </row>
     <row r="8" ht="160" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>7c(ii)</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>The University is playing a leading and convening role on sustainability challenges and opportunities internationally, with particular focus on vulnerable 
 and disadvantaged people in Asia and the Pacific</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>List of sustainability focused relationships and partnerships with overseas universities and organisations; 1-2 case studies of key partnerships</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>Strengthened engagement with the Pacific region
 Throughout 2025, the University strengthened its engagement with institutions and communities with our closest neighbours in the Pacific. Drawing on the expertise and focus of leading initiatives such as the Oceania Institute and Melbourne Climate Futures, the University continued to work with regional partners to address the distinct challenges faced by the Pacific region. 
@@ -1348,15 +1246,15 @@
 Key convening moments in 2025 have included the delivery of the Asia and the Pacific Outlook Series in Honiara, the Oceania Institute Conversations series in Melbourne and the inaugural Oceania Oration delivered by The Honourable Professor Biman Prasad, Deputy Prime Minister of Fiji in August. His address called for reframing perspectives on the Pacific, strengthening regional partnerships, and addressing climate and development challenges collaboratively.</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr"/>
-      <c r="H8" s="19" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr"/>
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>https://www.unimelb.edu.au/newsroom/news/2025/march/university-of-melbourne-leads-engagement-with-the-pacific-through-education-and-research
 https://www.unimelb.edu.au/newsroom/news/2025/february/university-of-melbourne-strengthens-ties-with-pacific
 https://www.unimelb.edu.au/newsroom/news/2025/august/university-of-melbourne-hosts-inaugural-oceania-oration-on-pacific-futures</t>
         </is>
       </c>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
@@ -1379,13 +1277,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I9"/>
+  <dimension ref="B1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>End 2026 target status</t>
+          <t>(not used – no target status rating in 2026)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -1401,21 +1299,6 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>Y/N</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Target status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Response count</t>
         </is>
       </c>
     </row>
@@ -1440,24 +1323,8 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
@@ -1473,24 +1340,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Partially – see comments</t>
@@ -1506,47 +1357,15 @@
           <t>TBC</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>First review</t>
@@ -1554,11 +1373,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Follow-up</t>

--- a/output/central_unit_requests/GCE - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/GCE - SR26 sustainability reporting request.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.14)</t>
+          <t>SR26 sustainability reporting (v0.15)</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/GCE - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/GCE - SR26 sustainability reporting request.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.15)</t>
+          <t>SR26 sustainability reporting (v0.16)</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/GCE - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/GCE - SR26 sustainability reporting request.xlsx
@@ -20,21 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="00002060"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -178,61 +170,59 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -620,32 +610,22 @@
     <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>SR26 sustainability reporting (v0.16)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>SR26 sustainability reporting request</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
@@ -661,244 +641,247 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8" ht="60" customHeight="1"/>
-    <row r="11">
-      <c r="B11" s="6" t="inlineStr">
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11" ht="39" customHeight="1">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>GCE – Global, Culture and Engagement</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="C13" s="7" t="inlineStr">
+    <row r="12"/>
+    <row r="13" ht="27" customHeight="1">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="8" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="9" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="10" t="inlineStr">
+      <c r="L14" s="8" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N14" s="10" t="inlineStr">
+      <c r="N14" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O14" s="10" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P14" s="10" t="inlineStr">
+      <c r="P14" s="8" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q14" s="10" t="inlineStr">
+      <c r="Q14" s="8" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="11" t="inlineStr"/>
-      <c r="C15" s="11" t="inlineStr"/>
-      <c r="D15" s="11" t="inlineStr"/>
-      <c r="E15" s="11" t="inlineStr"/>
-      <c r="F15" s="11" t="inlineStr"/>
-      <c r="G15" s="11" t="inlineStr"/>
-      <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="11" t="inlineStr"/>
-      <c r="K15" s="11" t="inlineStr"/>
-      <c r="L15" s="11" t="inlineStr">
+    <row r="15" ht="81" customHeight="1">
+      <c r="B15" s="9" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr"/>
+      <c r="G15" s="9" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr"/>
+      <c r="J15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P15" s="11" t="inlineStr">
+      <c r="P15" s="9" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q15" s="11" t="inlineStr">
+      <c r="Q15" s="9" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Evidence of sustainability outcomes informed by Indigenous knowledges</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>Please provide examples or case studies from your Faculty/Portfolio of sustainability outcomes informed by Indigenous knowledges. Describe the activity or decision, how Indigenous knowledges were incorporated or co-created, who was involved, and the resulting sustainability outcome.</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>We will report on the ways Indigenous knowledges inform sustainability activities across the University, and develop selected examples into case studies with appropriate permissions.</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr"/>
-      <c r="J16" s="14" t="inlineStr"/>
-      <c r="K16" s="14" t="inlineStr"/>
-      <c r="L16" s="15" t="n"/>
-      <c r="M16" s="15" t="n"/>
-      <c r="N16" s="15" t="n"/>
-      <c r="O16" s="15" t="n"/>
-      <c r="P16" s="15" t="n"/>
-      <c r="Q16" s="15" t="n"/>
-    </row>
-    <row r="17" ht="150" customHeight="1">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="I16" s="12" t="inlineStr"/>
+      <c r="J16" s="12" t="inlineStr"/>
+      <c r="K16" s="12" t="inlineStr"/>
+      <c r="L16" s="13" t="n"/>
+      <c r="M16" s="13" t="n"/>
+      <c r="N16" s="13" t="n"/>
+      <c r="O16" s="13" t="n"/>
+      <c r="P16" s="13" t="n"/>
+      <c r="Q16" s="13" t="n"/>
+    </row>
+    <row r="17" ht="204" customHeight="1">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your area reported on the related SP2030 target 7c(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>7c(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I17" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J17" s="14" t="inlineStr">
+      <c r="J17" s="12" t="inlineStr">
         <is>
           <t>Strengthened engagement with the Pacific region
 Throughout 2025, the University strengthened its engagement with institutions and communities with our closest neighbours in the Pacific. Drawing on the expertise and focus of leading initiatives such as the Oceania Institute and Melbourne Climate Futures, the University continued to work with regional partners to address the distinct challenges faced by the Pacific region. 
@@ -906,19 +889,19 @@
 Key convening moments in 2025 have included the delivery of the Asia and the Pacific Outlook Series in Honiara, the Oceania Institute Conversations series in Melbourne and the inaugural Oceania Oration delivered by The Honourable Professor Biman Prasad, Deputy Prime Minister of Fiji in August. His address called for reframing perspectives on the Pacific, strengthening regional partnerships, and addressing climate and development challenges collaboratively.</t>
         </is>
       </c>
-      <c r="K17" s="14" t="inlineStr">
+      <c r="K17" s="12" t="inlineStr">
         <is>
           <t>https://www.unimelb.edu.au/newsroom/news/2025/march/university-of-melbourne-leads-engagement-with-the-pacific-through-education-and-research
 https://www.unimelb.edu.au/newsroom/news/2025/february/university-of-melbourne-strengthens-ties-with-pacific
 https://www.unimelb.edu.au/newsroom/news/2025/august/university-of-melbourne-hosts-inaugural-oceania-oration-on-pacific-futures</t>
         </is>
       </c>
-      <c r="L17" s="15" t="n"/>
-      <c r="M17" s="15" t="n"/>
-      <c r="N17" s="15" t="n"/>
-      <c r="O17" s="15" t="n"/>
-      <c r="P17" s="15" t="n"/>
-      <c r="Q17" s="15" t="n"/>
+      <c r="L17" s="13" t="n"/>
+      <c r="M17" s="13" t="n"/>
+      <c r="N17" s="13" t="n"/>
+      <c r="O17" s="13" t="n"/>
+      <c r="P17" s="13" t="n"/>
+      <c r="Q17" s="13" t="n"/>
     </row>
     <row r="18"/>
   </sheetData>
@@ -962,110 +945,102 @@
     <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>SR26 sustainability reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Highlighted stories (optional)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="17" t="inlineStr">
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
         </is>
       </c>
     </row>
     <row r="6"/>
-    <row r="8">
-      <c r="B8" s="19" t="inlineStr">
+    <row r="7"/>
+    <row r="8" ht="39" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr"/>
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr"/>
+      <c r="F9" s="18" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="15" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="15" t="n"/>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="15" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1096,108 +1071,97 @@
     <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>End-2025 target status assessment and reporting (for reference)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Your SR25 responses – Global, Culture and Engagement (GCE)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="21" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="22" t="inlineStr">
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Chancellery Global, Culture and Engagement</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="9" t="inlineStr">
+    <row r="6" ht="42" customHeight="1">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="12" t="inlineStr">
+    <row r="7" ht="409" customHeight="1">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>7a</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>The University’s community partnerships demonstrate localised and co-created approaches to sustainability.</t>
         </is>
       </c>
-      <c r="D7" s="14" t="e">
+      <c r="D7" s="12" t="e">
         <v>#REF!</v>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>Grounded in hyper local collaboration and partnerships the University's civic and community initiatives respond to and address key issues identified by communities and includes the following. 
 *Co- leading  a five-year collective action initiative to address  food security challenges  in Carlton, co-designing and evaluating programs with residents and local organisations. 
@@ -1207,38 +1171,38 @@
  *Supporting  the digital equity initiative in collaboration with UoM E-Waste to donate a further 33 iPads to community organisations. Work is underway to expand this program with the support of Business Services.                                                                                                                     *Employing social procurement and sustainability practices in Civic and Community Engagement program delivery. E.g. Choose to Reuse, social enterprise catering, bicycle couriers, online presentations to offset travel.</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr"/>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr"/>
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>https://www.innercitynews.com.au/tackling-hunger-in-carlton/
 https://about.unimelb.edu.au/news-resources/awards-and-achievements/announcements/university-of-melbourne-and-carlton-community-partner-to-enhance-local-food-security/_recache</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr"/>
-    </row>
-    <row r="8" ht="160" customHeight="1">
-      <c r="B8" s="12" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr"/>
+    </row>
+    <row r="8" ht="402" customHeight="1">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>7c(ii)</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>The University is playing a leading and convening role on sustainability challenges and opportunities internationally, with particular focus on vulnerable 
 and disadvantaged people in Asia and the Pacific</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>List of sustainability focused relationships and partnerships with overseas universities and organisations; 1-2 case studies of key partnerships</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>Strengthened engagement with the Pacific region
 Throughout 2025, the University strengthened its engagement with institutions and communities with our closest neighbours in the Pacific. Drawing on the expertise and focus of leading initiatives such as the Oceania Institute and Melbourne Climate Futures, the University continued to work with regional partners to address the distinct challenges faced by the Pacific region. 
@@ -1246,15 +1210,15 @@
 Key convening moments in 2025 have included the delivery of the Asia and the Pacific Outlook Series in Honiara, the Oceania Institute Conversations series in Melbourne and the inaugural Oceania Oration delivered by The Honourable Professor Biman Prasad, Deputy Prime Minister of Fiji in August. His address called for reframing perspectives on the Pacific, strengthening regional partnerships, and addressing climate and development challenges collaboratively.</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr"/>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr"/>
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>https://www.unimelb.edu.au/newsroom/news/2025/march/university-of-melbourne-leads-engagement-with-the-pacific-through-education-and-research
 https://www.unimelb.edu.au/newsroom/news/2025/february/university-of-melbourne-strengthens-ties-with-pacific
 https://www.unimelb.edu.au/newsroom/news/2025/august/university-of-melbourne-hosts-inaugural-oceania-oration-on-pacific-futures</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
@@ -1277,10 +1241,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="B1" t="inlineStr">
         <is>
           <t>(not used – no target status rating in 2026)</t>
@@ -1302,7 +1273,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="22" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
           <t>Please select from dropdown</t>
@@ -1324,7 +1295,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="22" customHeight="1">
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
@@ -1341,7 +1312,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="22" customHeight="1">
       <c r="C4" t="inlineStr">
         <is>
           <t>Partially – see comments</t>
@@ -1358,35 +1329,35 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="22" customHeight="1">
       <c r="D5" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="22" customHeight="1">
       <c r="D6" t="inlineStr">
         <is>
           <t>First review</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="22" customHeight="1">
       <c r="D7" t="inlineStr">
         <is>
           <t>Follow-up</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="22" customHeight="1">
       <c r="D8" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="22" customHeight="1">
       <c r="D9" t="inlineStr">
         <is>
           <t>Not required</t>

--- a/output/central_unit_requests/GCE - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/GCE - SR26 sustainability reporting request.xlsx
@@ -633,7 +633,7 @@
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
-• Due: Tuesday 15 December 2026. Questions: CDSS – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
+• Due: Tuesday 15 December 2026. Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/GCE - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/GCE - SR26 sustainability reporting request.xlsx
@@ -31,7 +31,7 @@
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="00002060"/>
+      <color rgb="00FFFFFF"/>
       <sz val="22"/>
     </font>
     <font>
@@ -110,7 +110,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -135,6 +135,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00000F46"/>
       </patternFill>
     </fill>
   </fills>
@@ -170,9 +175,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="4"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -297,6 +305,96 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -588,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -608,24 +706,61 @@
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>SR26 sustainability reporting request</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
@@ -633,7 +768,7 @@
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
-• Due: Tuesday 15 December 2026. Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
+• Due: Thursday 24 December 2026 (Christmas shutdown). Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
     </row>
@@ -644,7 +779,7 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11" ht="39" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>GCE – Global, Culture and Engagement</t>
         </is>
@@ -652,236 +787,236 @@
     </row>
     <row r="12"/>
     <row r="13" ht="27" customHeight="1">
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="9" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P14" s="8" t="inlineStr">
+      <c r="P14" s="9" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q14" s="8" t="inlineStr">
+      <c r="Q14" s="9" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="81" customHeight="1">
-      <c r="B15" s="9" t="inlineStr"/>
-      <c r="C15" s="9" t="inlineStr"/>
-      <c r="D15" s="9" t="inlineStr"/>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="9" t="inlineStr"/>
-      <c r="G15" s="9" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr"/>
-      <c r="I15" s="9" t="inlineStr"/>
-      <c r="J15" s="9" t="inlineStr"/>
-      <c r="K15" s="9" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr"/>
+      <c r="C15" s="10" t="inlineStr"/>
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="10" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr"/>
+      <c r="J15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr"/>
+      <c r="L15" s="10" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M15" s="9" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O15" s="9" t="inlineStr">
+      <c r="O15" s="10" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P15" s="9" t="inlineStr">
+      <c r="P15" s="10" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q15" s="9" t="inlineStr">
+      <c r="Q15" s="10" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Evidence of sustainability outcomes informed by Indigenous knowledges</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>Please provide examples or case studies from your Faculty/Portfolio of sustainability outcomes informed by Indigenous knowledges. Describe the activity or decision, how Indigenous knowledges were incorporated or co-created, who was involved, and the resulting sustainability outcome.</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>We will report on the ways Indigenous knowledges inform sustainability activities across the University, and develop selected examples into case studies with appropriate permissions.</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I16" s="12" t="inlineStr"/>
-      <c r="J16" s="12" t="inlineStr"/>
-      <c r="K16" s="12" t="inlineStr"/>
-      <c r="L16" s="13" t="n"/>
-      <c r="M16" s="13" t="n"/>
-      <c r="N16" s="13" t="n"/>
-      <c r="O16" s="13" t="n"/>
-      <c r="P16" s="13" t="n"/>
-      <c r="Q16" s="13" t="n"/>
-    </row>
-    <row r="17" ht="204" customHeight="1">
-      <c r="B17" s="10" t="inlineStr">
+      <c r="I16" s="13" t="inlineStr"/>
+      <c r="J16" s="13" t="inlineStr"/>
+      <c r="K16" s="13" t="inlineStr"/>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
+      <c r="N16" s="14" t="n"/>
+      <c r="O16" s="14" t="n"/>
+      <c r="P16" s="14" t="n"/>
+      <c r="Q16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="171" customHeight="1">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your area reported on the related SP2030 target 7c(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.
+In end-2025 reporting your area reported on the related SP2030 target 7c(ii) (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
         <is>
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H17" s="15" t="inlineStr">
         <is>
           <t>7c(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr">
+      <c r="I17" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J17" s="12" t="inlineStr">
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t>Strengthened engagement with the Pacific region
 Throughout 2025, the University strengthened its engagement with institutions and communities with our closest neighbours in the Pacific. Drawing on the expertise and focus of leading initiatives such as the Oceania Institute and Melbourne Climate Futures, the University continued to work with regional partners to address the distinct challenges faced by the Pacific region. 
@@ -889,19 +1024,19 @@
 Key convening moments in 2025 have included the delivery of the Asia and the Pacific Outlook Series in Honiara, the Oceania Institute Conversations series in Melbourne and the inaugural Oceania Oration delivered by The Honourable Professor Biman Prasad, Deputy Prime Minister of Fiji in August. His address called for reframing perspectives on the Pacific, strengthening regional partnerships, and addressing climate and development challenges collaboratively.</t>
         </is>
       </c>
-      <c r="K17" s="12" t="inlineStr">
+      <c r="K17" s="13" t="inlineStr">
         <is>
           <t>https://www.unimelb.edu.au/newsroom/news/2025/march/university-of-melbourne-leads-engagement-with-the-pacific-through-education-and-research
 https://www.unimelb.edu.au/newsroom/news/2025/february/university-of-melbourne-strengthens-ties-with-pacific
 https://www.unimelb.edu.au/newsroom/news/2025/august/university-of-melbourne-hosts-inaugural-oceania-oration-on-pacific-futures</t>
         </is>
       </c>
-      <c r="L17" s="13" t="n"/>
-      <c r="M17" s="13" t="n"/>
-      <c r="N17" s="13" t="n"/>
-      <c r="O17" s="13" t="n"/>
-      <c r="P17" s="13" t="n"/>
-      <c r="Q17" s="13" t="n"/>
+      <c r="L17" s="14" t="n"/>
+      <c r="M17" s="14" t="n"/>
+      <c r="N17" s="14" t="n"/>
+      <c r="O17" s="14" t="n"/>
+      <c r="P17" s="14" t="n"/>
+      <c r="Q17" s="14" t="n"/>
     </row>
     <row r="18"/>
   </sheetData>
@@ -921,6 +1056,7 @@
     <hyperlink ref="H17" location="'3. SR25 responses'!B8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -930,7 +1066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -943,104 +1079,148 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Highlighted stories (optional)</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3"/>
     <row r="4"/>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Thursday 24 December 2026 (Christmas shutdown) (early submission helps us develop case studies).</t>
         </is>
       </c>
     </row>
     <row r="6"/>
     <row r="7"/>
     <row r="8" ht="39" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="18" t="inlineStr"/>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr"/>
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr"/>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr"/>
+      <c r="F9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1048,6 +1228,7 @@
     <mergeCell ref="C5:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1057,7 +1238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1069,99 +1250,144 @@
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Your SR25 responses – Global, Culture and Engagement (GCE)</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Chancellery Global, Culture and Engagement</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="409" customHeight="1">
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>7a</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>The University’s community partnerships demonstrate localised and co-created approaches to sustainability.</t>
         </is>
       </c>
-      <c r="D7" s="12" t="e">
+      <c r="D7" s="13" t="e">
         <v>#REF!</v>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>Grounded in hyper local collaboration and partnerships the University's civic and community initiatives respond to and address key issues identified by communities and includes the following. 
 *Co- leading  a five-year collective action initiative to address  food security challenges  in Carlton, co-designing and evaluating programs with residents and local organisations. 
@@ -1171,38 +1397,38 @@
  *Supporting  the digital equity initiative in collaboration with UoM E-Waste to donate a further 33 iPads to community organisations. Work is underway to expand this program with the support of Business Services.                                                                                                                     *Employing social procurement and sustainability practices in Civic and Community Engagement program delivery. E.g. Choose to Reuse, social enterprise catering, bicycle couriers, online presentations to offset travel.</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr"/>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>https://www.innercitynews.com.au/tackling-hunger-in-carlton/
 https://about.unimelb.edu.au/news-resources/awards-and-achievements/announcements/university-of-melbourne-and-carlton-community-partner-to-enhance-local-food-security/_recache</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr"/>
+      <c r="I7" s="13" t="inlineStr"/>
     </row>
     <row r="8" ht="402" customHeight="1">
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>7c(ii)</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>The University is playing a leading and convening role on sustainability challenges and opportunities internationally, with particular focus on vulnerable 
 and disadvantaged people in Asia and the Pacific</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>List of sustainability focused relationships and partnerships with overseas universities and organisations; 1-2 case studies of key partnerships</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>Strengthened engagement with the Pacific region
 Throughout 2025, the University strengthened its engagement with institutions and communities with our closest neighbours in the Pacific. Drawing on the expertise and focus of leading initiatives such as the Oceania Institute and Melbourne Climate Futures, the University continued to work with regional partners to address the distinct challenges faced by the Pacific region. 
@@ -1210,15 +1436,15 @@
 Key convening moments in 2025 have included the delivery of the Asia and the Pacific Outlook Series in Honiara, the Oceania Institute Conversations series in Melbourne and the inaugural Oceania Oration delivered by The Honourable Professor Biman Prasad, Deputy Prime Minister of Fiji in August. His address called for reframing perspectives on the Pacific, strengthening regional partnerships, and addressing climate and development challenges collaboratively.</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr"/>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr"/>
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>https://www.unimelb.edu.au/newsroom/news/2025/march/university-of-melbourne-leads-engagement-with-the-pacific-through-education-and-research
 https://www.unimelb.edu.au/newsroom/news/2025/february/university-of-melbourne-strengthens-ties-with-pacific
 https://www.unimelb.edu.au/newsroom/news/2025/august/university-of-melbourne-hosts-inaugural-oceania-oration-on-pacific-futures</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
@@ -1232,6 +1458,7 @@
     <hyperlink ref="B4" location="'1. Reporting template'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/output/central_unit_requests/GCE - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/GCE - SR26 sustainability reporting request.xlsx
@@ -703,9 +703,9 @@
     <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -764,7 +764,8 @@
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
-• Note the source of your information and any limitations (Column O), then confirm the information is accurate (Columns P–Q)
+• Note the source of your information, any limitations and the person closest to the data (Column O)
+• Please return the spreadsheet once it has been reviewed and confirmed by your area's senior lead
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
@@ -803,7 +804,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="42" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
@@ -871,17 +872,7 @@
       </c>
       <c r="O14" s="9" t="inlineStr">
         <is>
-          <t>Data source and limitations</t>
-        </is>
-      </c>
-      <c r="P14" s="9" t="inlineStr">
-        <is>
-          <t>Data owner confirms information is accurate</t>
-        </is>
-      </c>
-      <c r="Q14" s="9" t="inlineStr">
-        <is>
-          <t>Confirmed by (name, role, date)</t>
+          <t>Data source, limitations and contact person</t>
         </is>
       </c>
     </row>
@@ -913,17 +904,7 @@
       </c>
       <c r="O15" s="10" t="inlineStr">
         <is>
-          <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
-        </is>
-      </c>
-      <c r="P15" s="10" t="inlineStr">
-        <is>
-          <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
-        </is>
-      </c>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>Name, role and date of the person confirming</t>
+          <t>Where did this information come from (system, report, survey)? Note any gaps or limitations, and the person closest to the data we can follow up with.</t>
         </is>
       </c>
     </row>
@@ -950,7 +931,7 @@
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>Please provide examples or case studies from your Faculty/Portfolio of sustainability outcomes informed by Indigenous knowledges. Describe the activity or decision, how Indigenous knowledges were incorporated or co-created, who was involved, and the resulting sustainability outcome.</t>
+          <t>Please provide examples or case studies from your portfolio of sustainability outcomes informed by Indigenous knowledges. Describe the activity or decision, how Indigenous knowledges were incorporated or co-created, who was involved, and the resulting sustainability outcome.</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
@@ -970,10 +951,8 @@
       <c r="M16" s="14" t="n"/>
       <c r="N16" s="14" t="n"/>
       <c r="O16" s="14" t="n"/>
-      <c r="P16" s="14" t="n"/>
-      <c r="Q16" s="14" t="n"/>
-    </row>
-    <row r="17" ht="171" customHeight="1">
+    </row>
+    <row r="17" ht="154" customHeight="1">
       <c r="B17" s="11" t="inlineStr">
         <is>
           <t>EN1(c)</t>
@@ -996,13 +975,13 @@
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.
+          <t>Please provide examples of internal engagement or external partnerships involving your portfolio that contributed to sustainability outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.
 In end-2025 reporting your area reported on the related SP2030 target 7c(ii) (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
+          <t>We will report on internal engagement and partnerships contributing to sustainability outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
       <c r="H17" s="15" t="inlineStr">
@@ -1035,23 +1014,16 @@
       <c r="M17" s="14" t="n"/>
       <c r="N17" s="14" t="n"/>
       <c r="O17" s="14" t="n"/>
-      <c r="P17" s="14" t="n"/>
-      <c r="Q17" s="14" t="n"/>
     </row>
     <row r="18"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="4">
     <mergeCell ref="C13:G13"/>
-    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="L13:O13"/>
     <mergeCell ref="D4:G8"/>
     <mergeCell ref="B4:C8"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="P16:P17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$C$2:$C$4</formula1>
-    </dataValidation>
-  </dataValidations>
   <hyperlinks>
     <hyperlink ref="H17" location="'3. SR25 responses'!B8"/>
   </hyperlinks>
